--- a/output/yearly_population_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_58_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4086</v>
+        <v>5076</v>
       </c>
       <c r="C2" t="n">
-        <v>14408</v>
+        <v>6844</v>
       </c>
       <c r="D2" t="n">
-        <v>26962</v>
+        <v>21464</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2540</v>
+        <v>3388</v>
       </c>
       <c r="C3" t="n">
-        <v>8777</v>
+        <v>5926</v>
       </c>
       <c r="D3" t="n">
-        <v>19797</v>
+        <v>13744</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2178</v>
+        <v>2749</v>
       </c>
       <c r="C4" t="n">
-        <v>8934</v>
+        <v>5238</v>
       </c>
       <c r="D4" t="n">
-        <v>9383</v>
+        <v>7373</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1439</v>
+        <v>1754</v>
       </c>
       <c r="C5" t="n">
-        <v>6511</v>
+        <v>4990</v>
       </c>
       <c r="D5" t="n">
-        <v>3438</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>786</v>
+        <v>961</v>
       </c>
       <c r="C6" t="n">
-        <v>4320</v>
+        <v>3842</v>
       </c>
       <c r="D6" t="n">
-        <v>1350</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>454</v>
       </c>
       <c r="C7" t="n">
-        <v>2809</v>
+        <v>2168</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>1353</v>
+        <v>1065</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>498</v>
+        <v>451</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
         <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4081</v>
+        <v>5339</v>
       </c>
       <c r="C2" t="n">
-        <v>16858</v>
+        <v>12269</v>
       </c>
       <c r="D2" t="n">
-        <v>29744</v>
+        <v>25207</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2572</v>
+        <v>3356</v>
       </c>
       <c r="C3" t="n">
-        <v>9790</v>
+        <v>5586</v>
       </c>
       <c r="D3" t="n">
-        <v>19389</v>
+        <v>13830</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1988</v>
+        <v>2583</v>
       </c>
       <c r="C4" t="n">
-        <v>8596</v>
+        <v>5395</v>
       </c>
       <c r="D4" t="n">
-        <v>10507</v>
+        <v>8056</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1532</v>
+        <v>1918</v>
       </c>
       <c r="C5" t="n">
-        <v>7313</v>
+        <v>4950</v>
       </c>
       <c r="D5" t="n">
-        <v>4189</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>951</v>
+        <v>1175</v>
       </c>
       <c r="C6" t="n">
-        <v>5165</v>
+        <v>4312</v>
       </c>
       <c r="D6" t="n">
-        <v>1599</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>463</v>
+        <v>601</v>
       </c>
       <c r="C7" t="n">
-        <v>3372</v>
+        <v>2867</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="C8" t="n">
-        <v>1895</v>
+        <v>1529</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>816</v>
+        <v>693</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4478</v>
+        <v>7882</v>
       </c>
       <c r="C2" t="n">
-        <v>11452</v>
+        <v>17582</v>
       </c>
       <c r="D2" t="n">
-        <v>30323</v>
+        <v>26384</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2545</v>
+        <v>3381</v>
       </c>
       <c r="C3" t="n">
-        <v>11033</v>
+        <v>7321</v>
       </c>
       <c r="D3" t="n">
-        <v>19338</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1874</v>
+        <v>2466</v>
       </c>
       <c r="C4" t="n">
-        <v>8793</v>
+        <v>5311</v>
       </c>
       <c r="D4" t="n">
-        <v>11381</v>
+        <v>8565</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1518</v>
+        <v>1961</v>
       </c>
       <c r="C5" t="n">
-        <v>7641</v>
+        <v>5030</v>
       </c>
       <c r="D5" t="n">
-        <v>4809</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1053</v>
+        <v>1329</v>
       </c>
       <c r="C6" t="n">
-        <v>5837</v>
+        <v>4483</v>
       </c>
       <c r="D6" t="n">
-        <v>1901</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>567</v>
+        <v>735</v>
       </c>
       <c r="C7" t="n">
-        <v>3970</v>
+        <v>3404</v>
       </c>
       <c r="D7" t="n">
-        <v>840</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>251</v>
+        <v>337</v>
       </c>
       <c r="C8" t="n">
-        <v>2382</v>
+        <v>2039</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="C9" t="n">
-        <v>1167</v>
+        <v>989</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4236</v>
+        <v>7091</v>
       </c>
       <c r="C2" t="n">
-        <v>8337</v>
+        <v>12237</v>
       </c>
       <c r="D2" t="n">
-        <v>25372</v>
+        <v>21794</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3114</v>
+        <v>4203</v>
       </c>
       <c r="C3" t="n">
-        <v>15468</v>
+        <v>11100</v>
       </c>
       <c r="D3" t="n">
-        <v>21165</v>
+        <v>15681</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1402</v>
+        <v>1811</v>
       </c>
       <c r="C4" t="n">
-        <v>11724</v>
+        <v>7683</v>
       </c>
       <c r="D4" t="n">
-        <v>10627</v>
+        <v>8380</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>972</v>
+        <v>1227</v>
       </c>
       <c r="C5" t="n">
-        <v>5720</v>
+        <v>4393</v>
       </c>
       <c r="D5" t="n">
-        <v>3063</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>523</v>
+        <v>679</v>
       </c>
       <c r="C6" t="n">
-        <v>3890</v>
+        <v>3335</v>
       </c>
       <c r="D6" t="n">
-        <v>823</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>231</v>
+        <v>311</v>
       </c>
       <c r="C7" t="n">
-        <v>2334</v>
+        <v>1998</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>1143</v>
+        <v>969</v>
       </c>
       <c r="D8" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="D9" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2625</v>
+        <v>4247</v>
       </c>
       <c r="C2" t="n">
-        <v>4495</v>
+        <v>5620</v>
       </c>
       <c r="D2" t="n">
-        <v>17790</v>
+        <v>15487</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3077</v>
+        <v>4611</v>
       </c>
       <c r="C3" t="n">
-        <v>11450</v>
+        <v>10542</v>
       </c>
       <c r="D3" t="n">
-        <v>20721</v>
+        <v>15759</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1739</v>
+        <v>2354</v>
       </c>
       <c r="C4" t="n">
-        <v>13511</v>
+        <v>9286</v>
       </c>
       <c r="D4" t="n">
-        <v>11924</v>
+        <v>9257</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1059</v>
+        <v>1368</v>
       </c>
       <c r="C5" t="n">
-        <v>8010</v>
+        <v>5839</v>
       </c>
       <c r="D5" t="n">
-        <v>3827</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>605</v>
+        <v>797</v>
       </c>
       <c r="C6" t="n">
-        <v>4692</v>
+        <v>3894</v>
       </c>
       <c r="D6" t="n">
-        <v>1009</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>212</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>2866</v>
+        <v>2494</v>
       </c>
       <c r="D7" t="n">
         <v>507</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>1467</v>
+        <v>1277</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2123</v>
+        <v>4024</v>
       </c>
       <c r="C2" t="n">
-        <v>4694</v>
+        <v>6809</v>
       </c>
       <c r="D2" t="n">
-        <v>23843</v>
+        <v>15273</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2470</v>
+        <v>3784</v>
       </c>
       <c r="C3" t="n">
-        <v>7625</v>
+        <v>7353</v>
       </c>
       <c r="D3" t="n">
-        <v>18986</v>
+        <v>14663</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1933</v>
+        <v>2814</v>
       </c>
       <c r="C4" t="n">
-        <v>12319</v>
+        <v>9695</v>
       </c>
       <c r="D4" t="n">
-        <v>12912</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1183</v>
+        <v>1583</v>
       </c>
       <c r="C5" t="n">
-        <v>10167</v>
+        <v>7361</v>
       </c>
       <c r="D5" t="n">
-        <v>4876</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>710</v>
+        <v>943</v>
       </c>
       <c r="C6" t="n">
-        <v>5988</v>
+        <v>4697</v>
       </c>
       <c r="D6" t="n">
-        <v>1374</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="7">
@@ -2405,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>428</v>
       </c>
       <c r="C7" t="n">
-        <v>3608</v>
+        <v>3107</v>
       </c>
       <c r="D7" t="n">
         <v>565</v>
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
-        <v>1988</v>
+        <v>1766</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>809</v>
+        <v>768</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1318</v>
+        <v>2408</v>
       </c>
       <c r="C2" t="n">
-        <v>2391</v>
+        <v>3264</v>
       </c>
       <c r="D2" t="n">
-        <v>16865</v>
+        <v>10638</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2322</v>
+        <v>3738</v>
       </c>
       <c r="C3" t="n">
-        <v>6586</v>
+        <v>6962</v>
       </c>
       <c r="D3" t="n">
-        <v>19057</v>
+        <v>14397</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2098</v>
+        <v>3091</v>
       </c>
       <c r="C4" t="n">
-        <v>11938</v>
+        <v>9682</v>
       </c>
       <c r="D4" t="n">
-        <v>13746</v>
+        <v>10652</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1224</v>
+        <v>1652</v>
       </c>
       <c r="C5" t="n">
-        <v>12260</v>
+        <v>9060</v>
       </c>
       <c r="D5" t="n">
-        <v>4950</v>
+        <v>4422</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>547</v>
+        <v>770</v>
       </c>
       <c r="C6" t="n">
-        <v>6687</v>
+        <v>5598</v>
       </c>
       <c r="D6" t="n">
-        <v>1328</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>3649</v>
+        <v>3221</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1318</v>
+        <v>1271</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1711</v>
+        <v>2638</v>
       </c>
       <c r="C2" t="n">
-        <v>4094</v>
+        <v>7018</v>
       </c>
       <c r="D2" t="n">
-        <v>14100</v>
+        <v>11150</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1676</v>
+        <v>2745</v>
       </c>
       <c r="C3" t="n">
-        <v>4401</v>
+        <v>4754</v>
       </c>
       <c r="D3" t="n">
-        <v>17574</v>
+        <v>12971</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1907</v>
+        <v>2922</v>
       </c>
       <c r="C4" t="n">
-        <v>9429</v>
+        <v>8320</v>
       </c>
       <c r="D4" t="n">
-        <v>14092</v>
+        <v>10903</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1386</v>
+        <v>1974</v>
       </c>
       <c r="C5" t="n">
-        <v>11992</v>
+        <v>9140</v>
       </c>
       <c r="D5" t="n">
-        <v>5981</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>8784</v>
+        <v>7086</v>
       </c>
       <c r="D6" t="n">
-        <v>1776</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>189</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>4755</v>
+        <v>4159</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>2110</v>
+        <v>1983</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>582</v>
+        <v>621</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1058</v>
+        <v>1781</v>
       </c>
       <c r="C2" t="n">
-        <v>2943</v>
+        <v>3726</v>
       </c>
       <c r="D2" t="n">
-        <v>10592</v>
+        <v>8758</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1481</v>
+        <v>2378</v>
       </c>
       <c r="C3" t="n">
-        <v>3971</v>
+        <v>5106</v>
       </c>
       <c r="D3" t="n">
-        <v>16312</v>
+        <v>12082</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1703</v>
+        <v>2644</v>
       </c>
       <c r="C4" t="n">
-        <v>7627</v>
+        <v>6982</v>
       </c>
       <c r="D4" t="n">
-        <v>14200</v>
+        <v>10934</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1457</v>
+        <v>2127</v>
       </c>
       <c r="C5" t="n">
-        <v>11391</v>
+        <v>9017</v>
       </c>
       <c r="D5" t="n">
-        <v>6692</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>787</v>
+        <v>1165</v>
       </c>
       <c r="C6" t="n">
-        <v>9994</v>
+        <v>7979</v>
       </c>
       <c r="D6" t="n">
-        <v>2072</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>5868</v>
+        <v>5061</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2631</v>
+        <v>2532</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>571</v>
+        <v>680</v>
       </c>
       <c r="D9" t="n">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1022</v>
+        <v>3125</v>
       </c>
       <c r="C2" t="n">
-        <v>7098</v>
+        <v>13365</v>
       </c>
       <c r="D2" t="n">
-        <v>13452</v>
+        <v>8485</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1137</v>
+        <v>1829</v>
       </c>
       <c r="C3" t="n">
-        <v>3267</v>
+        <v>4075</v>
       </c>
       <c r="D3" t="n">
-        <v>14725</v>
+        <v>11025</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1419</v>
+        <v>2240</v>
       </c>
       <c r="C4" t="n">
-        <v>6099</v>
+        <v>6062</v>
       </c>
       <c r="D4" t="n">
-        <v>13895</v>
+        <v>10650</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1418</v>
+        <v>2096</v>
       </c>
       <c r="C5" t="n">
-        <v>9707</v>
+        <v>8028</v>
       </c>
       <c r="D5" t="n">
-        <v>7425</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>916</v>
+        <v>1375</v>
       </c>
       <c r="C6" t="n">
-        <v>10400</v>
+        <v>8302</v>
       </c>
       <c r="D6" t="n">
-        <v>2578</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="C7" t="n">
-        <v>7297</v>
+        <v>6166</v>
       </c>
       <c r="D7" t="n">
-        <v>846</v>
+        <v>858</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>3613</v>
+        <v>3373</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1161</v>
+        <v>1267</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4676</v>
+        <v>5560</v>
       </c>
       <c r="C2" t="n">
-        <v>15555</v>
+        <v>11760</v>
       </c>
       <c r="D2" t="n">
-        <v>24446</v>
+        <v>7260</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>761</v>
+        <v>2284</v>
       </c>
       <c r="C2" t="n">
-        <v>4315</v>
+        <v>7805</v>
       </c>
       <c r="D2" t="n">
-        <v>10115</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1521</v>
+        <v>2527</v>
       </c>
       <c r="C3" t="n">
-        <v>4545</v>
+        <v>6446</v>
       </c>
       <c r="D3" t="n">
-        <v>15982</v>
+        <v>11877</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>3081</v>
       </c>
       <c r="C4" t="n">
-        <v>9256</v>
+        <v>8791</v>
       </c>
       <c r="D4" t="n">
-        <v>13991</v>
+        <v>10907</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>846</v>
+        <v>1289</v>
       </c>
       <c r="C5" t="n">
-        <v>14533</v>
+        <v>11758</v>
       </c>
       <c r="D5" t="n">
-        <v>6588</v>
+        <v>5711</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>272</v>
+        <v>432</v>
       </c>
       <c r="C6" t="n">
-        <v>8679</v>
+        <v>7507</v>
       </c>
       <c r="D6" t="n">
-        <v>1942</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>3540</v>
+        <v>3305</v>
       </c>
       <c r="D7" t="n">
-        <v>506</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1137</v>
+        <v>1241</v>
       </c>
       <c r="D8" t="n">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="D9" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5880</v>
+        <v>6401</v>
       </c>
       <c r="C2" t="n">
-        <v>11709</v>
+        <v>5127</v>
       </c>
       <c r="D2" t="n">
-        <v>26765</v>
+        <v>20179</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1950</v>
+        <v>2363</v>
       </c>
       <c r="C3" t="n">
-        <v>7839</v>
+        <v>5927</v>
       </c>
       <c r="D3" t="n">
-        <v>4746</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,10 +4596,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D8" t="n">
         <v>429</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
         <v>154</v>
@@ -4658,7 +4658,7 @@
         <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -4672,7 +4672,7 @@
         <v>92</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4694,7 +4694,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>73</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4214</v>
+        <v>5020</v>
       </c>
       <c r="C2" t="n">
-        <v>6858</v>
+        <v>5328</v>
       </c>
       <c r="D2" t="n">
-        <v>27436</v>
+        <v>27134</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3182</v>
+        <v>3598</v>
       </c>
       <c r="C3" t="n">
-        <v>8630</v>
+        <v>4721</v>
       </c>
       <c r="D3" t="n">
-        <v>7927</v>
+        <v>4799</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>865</v>
+        <v>1061</v>
       </c>
       <c r="C4" t="n">
-        <v>4561</v>
+        <v>3516</v>
       </c>
       <c r="D4" t="n">
-        <v>2092</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4952,10 +4952,10 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4348</v>
+        <v>4798</v>
       </c>
       <c r="C2" t="n">
-        <v>6610</v>
+        <v>12345</v>
       </c>
       <c r="D2" t="n">
-        <v>26476</v>
+        <v>27739</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3027</v>
+        <v>3531</v>
       </c>
       <c r="C3" t="n">
-        <v>6689</v>
+        <v>4375</v>
       </c>
       <c r="D3" t="n">
-        <v>10334</v>
+        <v>8027</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1699</v>
+        <v>1981</v>
       </c>
       <c r="C4" t="n">
-        <v>6648</v>
+        <v>4080</v>
       </c>
       <c r="D4" t="n">
-        <v>3072</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>403</v>
+        <v>487</v>
       </c>
       <c r="C5" t="n">
-        <v>2551</v>
+        <v>2020</v>
       </c>
       <c r="D5" t="n">
-        <v>1324</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5364,7 +5364,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5403,7 +5403,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4819</v>
+        <v>5407</v>
       </c>
       <c r="C2" t="n">
-        <v>12598</v>
+        <v>9781</v>
       </c>
       <c r="D2" t="n">
-        <v>32684</v>
+        <v>27306</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2983</v>
+        <v>3390</v>
       </c>
       <c r="C3" t="n">
-        <v>5809</v>
+        <v>7321</v>
       </c>
       <c r="D3" t="n">
-        <v>11947</v>
+        <v>10458</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1985</v>
+        <v>2312</v>
       </c>
       <c r="C4" t="n">
-        <v>6530</v>
+        <v>4111</v>
       </c>
       <c r="D4" t="n">
-        <v>4203</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>838</v>
+        <v>1016</v>
       </c>
       <c r="C5" t="n">
-        <v>4518</v>
+        <v>3045</v>
       </c>
       <c r="D5" t="n">
-        <v>1585</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="C6" t="n">
-        <v>1403</v>
+        <v>1157</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5714,7 +5714,7 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5568</v>
+        <v>6810</v>
       </c>
       <c r="C2" t="n">
-        <v>15053</v>
+        <v>5174</v>
       </c>
       <c r="D2" t="n">
-        <v>44456</v>
+        <v>21844</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2780</v>
+        <v>3156</v>
       </c>
       <c r="C3" t="n">
-        <v>7450</v>
+        <v>7012</v>
       </c>
       <c r="D3" t="n">
-        <v>13261</v>
+        <v>11555</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1523</v>
+        <v>1747</v>
       </c>
       <c r="C4" t="n">
-        <v>4972</v>
+        <v>4785</v>
       </c>
       <c r="D4" t="n">
-        <v>4680</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>713</v>
+        <v>864</v>
       </c>
       <c r="C5" t="n">
-        <v>4020</v>
+        <v>2592</v>
       </c>
       <c r="D5" t="n">
-        <v>1611</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>246</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>1929</v>
+        <v>1407</v>
       </c>
       <c r="D6" t="n">
-        <v>797</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>541</v>
+        <v>468</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>78</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3877</v>
+        <v>5333</v>
       </c>
       <c r="C2" t="n">
-        <v>13574</v>
+        <v>6997</v>
       </c>
       <c r="D2" t="n">
-        <v>34420</v>
+        <v>22942</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3411</v>
+        <v>4123</v>
       </c>
       <c r="C3" t="n">
-        <v>10086</v>
+        <v>5124</v>
       </c>
       <c r="D3" t="n">
-        <v>17297</v>
+        <v>12433</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1859</v>
+        <v>2142</v>
       </c>
       <c r="C4" t="n">
-        <v>6295</v>
+        <v>6010</v>
       </c>
       <c r="D4" t="n">
-        <v>6140</v>
+        <v>5264</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>972</v>
+        <v>1151</v>
       </c>
       <c r="C5" t="n">
-        <v>4466</v>
+        <v>3776</v>
       </c>
       <c r="D5" t="n">
-        <v>2151</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>434</v>
+        <v>537</v>
       </c>
       <c r="C6" t="n">
-        <v>3030</v>
+        <v>2061</v>
       </c>
       <c r="D6" t="n">
-        <v>934</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>1270</v>
+        <v>992</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>387</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3108</v>
+        <v>4375</v>
       </c>
       <c r="C2" t="n">
-        <v>9492</v>
+        <v>8326</v>
       </c>
       <c r="D2" t="n">
-        <v>35145</v>
+        <v>22532</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3025</v>
+        <v>3874</v>
       </c>
       <c r="C3" t="n">
-        <v>10329</v>
+        <v>5312</v>
       </c>
       <c r="D3" t="n">
-        <v>18848</v>
+        <v>13338</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2194</v>
+        <v>2671</v>
       </c>
       <c r="C4" t="n">
-        <v>8165</v>
+        <v>5391</v>
       </c>
       <c r="D4" t="n">
-        <v>7822</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1208</v>
+        <v>1424</v>
       </c>
       <c r="C5" t="n">
-        <v>5303</v>
+        <v>4898</v>
       </c>
       <c r="D5" t="n">
-        <v>2774</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>622</v>
+        <v>761</v>
       </c>
       <c r="C6" t="n">
-        <v>3671</v>
+        <v>2926</v>
       </c>
       <c r="D6" t="n">
-        <v>1110</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>307</v>
       </c>
       <c r="C7" t="n">
-        <v>2131</v>
+        <v>1526</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>802</v>
+        <v>672</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
         <v>239</v>
@@ -6507,7 +6507,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6636,7 +6636,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_58_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5076</v>
+        <v>6070</v>
       </c>
       <c r="C2" t="n">
-        <v>6844</v>
+        <v>9779</v>
       </c>
       <c r="D2" t="n">
-        <v>21464</v>
+        <v>26980</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3388</v>
+        <v>3589</v>
       </c>
       <c r="C3" t="n">
-        <v>5926</v>
+        <v>7191</v>
       </c>
       <c r="D3" t="n">
-        <v>13744</v>
+        <v>19122</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2749</v>
+        <v>3034</v>
       </c>
       <c r="C4" t="n">
-        <v>5238</v>
+        <v>5799</v>
       </c>
       <c r="D4" t="n">
-        <v>7373</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1754</v>
+        <v>1920</v>
       </c>
       <c r="C5" t="n">
-        <v>4990</v>
+        <v>4235</v>
       </c>
       <c r="D5" t="n">
-        <v>2881</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>961</v>
+        <v>1025</v>
       </c>
       <c r="C6" t="n">
-        <v>3842</v>
+        <v>2463</v>
       </c>
       <c r="D6" t="n">
-        <v>1188</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C7" t="n">
-        <v>2168</v>
+        <v>1541</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C8" t="n">
-        <v>1065</v>
+        <v>705</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>451</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5339</v>
+        <v>7427</v>
       </c>
       <c r="C2" t="n">
-        <v>12269</v>
+        <v>8159</v>
       </c>
       <c r="D2" t="n">
-        <v>25207</v>
+        <v>25102</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3356</v>
+        <v>3813</v>
       </c>
       <c r="C3" t="n">
-        <v>5586</v>
+        <v>7363</v>
       </c>
       <c r="D3" t="n">
-        <v>13830</v>
+        <v>18905</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2583</v>
+        <v>2809</v>
       </c>
       <c r="C4" t="n">
-        <v>5395</v>
+        <v>6290</v>
       </c>
       <c r="D4" t="n">
-        <v>8056</v>
+        <v>9256</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1918</v>
+        <v>2142</v>
       </c>
       <c r="C5" t="n">
-        <v>4950</v>
+        <v>4882</v>
       </c>
       <c r="D5" t="n">
-        <v>3483</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1175</v>
+        <v>1279</v>
       </c>
       <c r="C6" t="n">
-        <v>4312</v>
+        <v>3214</v>
       </c>
       <c r="D6" t="n">
-        <v>1404</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>601</v>
+        <v>628</v>
       </c>
       <c r="C7" t="n">
-        <v>2867</v>
+        <v>1956</v>
       </c>
       <c r="D7" t="n">
-        <v>723</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="C8" t="n">
-        <v>1529</v>
+        <v>1058</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>693</v>
+        <v>483</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>312</v>
+        <v>254</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
         <v>163</v>
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7882</v>
+        <v>9648</v>
       </c>
       <c r="C2" t="n">
-        <v>17582</v>
+        <v>9882</v>
       </c>
       <c r="D2" t="n">
-        <v>26384</v>
+        <v>32638</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3381</v>
+        <v>4271</v>
       </c>
       <c r="C3" t="n">
-        <v>7321</v>
+        <v>6819</v>
       </c>
       <c r="D3" t="n">
-        <v>14310</v>
+        <v>18458</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2466</v>
+        <v>2742</v>
       </c>
       <c r="C4" t="n">
-        <v>5311</v>
+        <v>6633</v>
       </c>
       <c r="D4" t="n">
-        <v>8565</v>
+        <v>10456</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1961</v>
+        <v>2152</v>
       </c>
       <c r="C5" t="n">
-        <v>5030</v>
+        <v>5328</v>
       </c>
       <c r="D5" t="n">
-        <v>4035</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1329</v>
+        <v>1480</v>
       </c>
       <c r="C6" t="n">
-        <v>4483</v>
+        <v>3842</v>
       </c>
       <c r="D6" t="n">
-        <v>1651</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>735</v>
+        <v>802</v>
       </c>
       <c r="C7" t="n">
-        <v>3404</v>
+        <v>2473</v>
       </c>
       <c r="D7" t="n">
-        <v>809</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C8" t="n">
-        <v>2039</v>
+        <v>1399</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>989</v>
+        <v>697</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>443</v>
+        <v>339</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7091</v>
+        <v>8674</v>
       </c>
       <c r="C2" t="n">
-        <v>12237</v>
+        <v>6719</v>
       </c>
       <c r="D2" t="n">
-        <v>21794</v>
+        <v>26819</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4203</v>
+        <v>5028</v>
       </c>
       <c r="C3" t="n">
-        <v>11100</v>
+        <v>10406</v>
       </c>
       <c r="D3" t="n">
-        <v>15681</v>
+        <v>20222</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1811</v>
+        <v>1988</v>
       </c>
       <c r="C4" t="n">
-        <v>7683</v>
+        <v>8808</v>
       </c>
       <c r="D4" t="n">
-        <v>8380</v>
+        <v>9584</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1227</v>
+        <v>1367</v>
       </c>
       <c r="C5" t="n">
-        <v>4393</v>
+        <v>3765</v>
       </c>
       <c r="D5" t="n">
-        <v>2702</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>679</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>3335</v>
+        <v>2423</v>
       </c>
       <c r="D6" t="n">
-        <v>792</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>1998</v>
+        <v>1371</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>969</v>
+        <v>683</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>434</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4247</v>
+        <v>5228</v>
       </c>
       <c r="C2" t="n">
-        <v>5620</v>
+        <v>3700</v>
       </c>
       <c r="D2" t="n">
-        <v>15487</v>
+        <v>18486</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4611</v>
+        <v>5603</v>
       </c>
       <c r="C3" t="n">
-        <v>10542</v>
+        <v>7989</v>
       </c>
       <c r="D3" t="n">
-        <v>15759</v>
+        <v>19954</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2354</v>
+        <v>2726</v>
       </c>
       <c r="C4" t="n">
-        <v>9286</v>
+        <v>9614</v>
       </c>
       <c r="D4" t="n">
-        <v>9257</v>
+        <v>11110</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1368</v>
+        <v>1522</v>
       </c>
       <c r="C5" t="n">
-        <v>5839</v>
+        <v>5949</v>
       </c>
       <c r="D5" t="n">
-        <v>3406</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>797</v>
+        <v>882</v>
       </c>
       <c r="C6" t="n">
-        <v>3894</v>
+        <v>3010</v>
       </c>
       <c r="D6" t="n">
-        <v>970</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>2494</v>
+        <v>1780</v>
       </c>
       <c r="D7" t="n">
-        <v>507</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>1277</v>
+        <v>900</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>473</v>
+        <v>377</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4024</v>
+        <v>4506</v>
       </c>
       <c r="C2" t="n">
-        <v>6809</v>
+        <v>7371</v>
       </c>
       <c r="D2" t="n">
-        <v>15273</v>
+        <v>18650</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3784</v>
+        <v>4614</v>
       </c>
       <c r="C3" t="n">
-        <v>7353</v>
+        <v>5297</v>
       </c>
       <c r="D3" t="n">
-        <v>14663</v>
+        <v>18413</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2814</v>
+        <v>3373</v>
       </c>
       <c r="C4" t="n">
-        <v>9695</v>
+        <v>8618</v>
       </c>
       <c r="D4" t="n">
-        <v>10036</v>
+        <v>12215</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1583</v>
+        <v>1805</v>
       </c>
       <c r="C5" t="n">
-        <v>7361</v>
+        <v>7606</v>
       </c>
       <c r="D5" t="n">
-        <v>4201</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>943</v>
+        <v>1060</v>
       </c>
       <c r="C6" t="n">
-        <v>4697</v>
+        <v>4278</v>
       </c>
       <c r="D6" t="n">
-        <v>1307</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>428</v>
+        <v>463</v>
       </c>
       <c r="C7" t="n">
-        <v>3107</v>
+        <v>2327</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C8" t="n">
-        <v>1766</v>
+        <v>1262</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>768</v>
+        <v>575</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2408</v>
+        <v>2685</v>
       </c>
       <c r="C2" t="n">
-        <v>3264</v>
+        <v>3458</v>
       </c>
       <c r="D2" t="n">
-        <v>10638</v>
+        <v>13031</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3738</v>
+        <v>4465</v>
       </c>
       <c r="C3" t="n">
-        <v>6962</v>
+        <v>5832</v>
       </c>
       <c r="D3" t="n">
-        <v>14397</v>
+        <v>18025</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3091</v>
+        <v>3718</v>
       </c>
       <c r="C4" t="n">
-        <v>9682</v>
+        <v>8182</v>
       </c>
       <c r="D4" t="n">
-        <v>10652</v>
+        <v>13008</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1652</v>
+        <v>1882</v>
       </c>
       <c r="C5" t="n">
-        <v>9060</v>
+        <v>9008</v>
       </c>
       <c r="D5" t="n">
-        <v>4422</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>770</v>
+        <v>858</v>
       </c>
       <c r="C6" t="n">
-        <v>5598</v>
+        <v>5058</v>
       </c>
       <c r="D6" t="n">
-        <v>1278</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>3221</v>
+        <v>2381</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1271</v>
+        <v>946</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2638</v>
+        <v>2989</v>
       </c>
       <c r="C2" t="n">
-        <v>7018</v>
+        <v>4380</v>
       </c>
       <c r="D2" t="n">
-        <v>11150</v>
+        <v>22193</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2745</v>
+        <v>3201</v>
       </c>
       <c r="C3" t="n">
-        <v>4754</v>
+        <v>4238</v>
       </c>
       <c r="D3" t="n">
-        <v>12971</v>
+        <v>16307</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2922</v>
+        <v>3542</v>
       </c>
       <c r="C4" t="n">
-        <v>8320</v>
+        <v>6984</v>
       </c>
       <c r="D4" t="n">
-        <v>10903</v>
+        <v>13383</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1974</v>
+        <v>2308</v>
       </c>
       <c r="C5" t="n">
-        <v>9140</v>
+        <v>8542</v>
       </c>
       <c r="D5" t="n">
-        <v>5184</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>1117</v>
       </c>
       <c r="C6" t="n">
-        <v>7086</v>
+        <v>6692</v>
       </c>
       <c r="D6" t="n">
-        <v>1696</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>4159</v>
+        <v>3476</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1983</v>
+        <v>1470</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>621</v>
+        <v>492</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1781</v>
+        <v>2323</v>
       </c>
       <c r="C2" t="n">
-        <v>3726</v>
+        <v>2989</v>
       </c>
       <c r="D2" t="n">
-        <v>8758</v>
+        <v>16094</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2378</v>
+        <v>2745</v>
       </c>
       <c r="C3" t="n">
-        <v>5106</v>
+        <v>3901</v>
       </c>
       <c r="D3" t="n">
-        <v>12082</v>
+        <v>16282</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2644</v>
+        <v>3172</v>
       </c>
       <c r="C4" t="n">
-        <v>6982</v>
+        <v>5932</v>
       </c>
       <c r="D4" t="n">
-        <v>10934</v>
+        <v>13469</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2127</v>
+        <v>2540</v>
       </c>
       <c r="C5" t="n">
-        <v>9017</v>
+        <v>8138</v>
       </c>
       <c r="D5" t="n">
-        <v>5729</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1165</v>
+        <v>1311</v>
       </c>
       <c r="C6" t="n">
-        <v>7979</v>
+        <v>7526</v>
       </c>
       <c r="D6" t="n">
-        <v>1977</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>5061</v>
+        <v>4469</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2532</v>
+        <v>1918</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>680</v>
+        <v>561</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3125</v>
+        <v>3602</v>
       </c>
       <c r="C2" t="n">
-        <v>13365</v>
+        <v>10020</v>
       </c>
       <c r="D2" t="n">
-        <v>8485</v>
+        <v>13069</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1829</v>
+        <v>2189</v>
       </c>
       <c r="C3" t="n">
-        <v>4075</v>
+        <v>3186</v>
       </c>
       <c r="D3" t="n">
-        <v>11025</v>
+        <v>15217</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2240</v>
+        <v>2629</v>
       </c>
       <c r="C4" t="n">
-        <v>6062</v>
+        <v>4913</v>
       </c>
       <c r="D4" t="n">
-        <v>10650</v>
+        <v>13464</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2096</v>
+        <v>2534</v>
       </c>
       <c r="C5" t="n">
-        <v>8028</v>
+        <v>7079</v>
       </c>
       <c r="D5" t="n">
-        <v>6254</v>
+        <v>7220</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1375</v>
+        <v>1576</v>
       </c>
       <c r="C6" t="n">
-        <v>8302</v>
+        <v>7771</v>
       </c>
       <c r="D6" t="n">
-        <v>2419</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>468</v>
+        <v>538</v>
       </c>
       <c r="C7" t="n">
-        <v>6166</v>
+        <v>5575</v>
       </c>
       <c r="D7" t="n">
-        <v>858</v>
+        <v>885</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>3373</v>
+        <v>2792</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1267</v>
+        <v>1005</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5560</v>
+        <v>5211</v>
       </c>
       <c r="C2" t="n">
-        <v>11760</v>
+        <v>4525</v>
       </c>
       <c r="D2" t="n">
-        <v>7260</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2284</v>
+        <v>2606</v>
       </c>
       <c r="C2" t="n">
-        <v>7805</v>
+        <v>5771</v>
       </c>
       <c r="D2" t="n">
-        <v>6312</v>
+        <v>9723</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2527</v>
+        <v>3004</v>
       </c>
       <c r="C3" t="n">
-        <v>6446</v>
+        <v>4997</v>
       </c>
       <c r="D3" t="n">
-        <v>11877</v>
+        <v>16244</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3081</v>
+        <v>3683</v>
       </c>
       <c r="C4" t="n">
-        <v>8791</v>
+        <v>7264</v>
       </c>
       <c r="D4" t="n">
-        <v>10907</v>
+        <v>13753</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1289</v>
+        <v>1503</v>
       </c>
       <c r="C5" t="n">
-        <v>11758</v>
+        <v>10721</v>
       </c>
       <c r="D5" t="n">
-        <v>5711</v>
+        <v>6477</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>432</v>
+        <v>497</v>
       </c>
       <c r="C6" t="n">
-        <v>7507</v>
+        <v>6910</v>
       </c>
       <c r="D6" t="n">
-        <v>1893</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>3305</v>
+        <v>2736</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1241</v>
+        <v>984</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6401</v>
+        <v>5818</v>
       </c>
       <c r="C2" t="n">
-        <v>5127</v>
+        <v>5210</v>
       </c>
       <c r="D2" t="n">
-        <v>20179</v>
+        <v>10275</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2363</v>
+        <v>2215</v>
       </c>
       <c r="C3" t="n">
-        <v>5927</v>
+        <v>2316</v>
       </c>
       <c r="D3" t="n">
-        <v>1859</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5020</v>
+        <v>5155</v>
       </c>
       <c r="C2" t="n">
-        <v>5328</v>
+        <v>6549</v>
       </c>
       <c r="D2" t="n">
-        <v>27134</v>
+        <v>16325</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3598</v>
+        <v>3298</v>
       </c>
       <c r="C3" t="n">
-        <v>4721</v>
+        <v>3429</v>
       </c>
       <c r="D3" t="n">
-        <v>4799</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1061</v>
+        <v>996</v>
       </c>
       <c r="C4" t="n">
-        <v>3516</v>
+        <v>1422</v>
       </c>
       <c r="D4" t="n">
-        <v>1555</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4798</v>
+        <v>4569</v>
       </c>
       <c r="C2" t="n">
-        <v>12345</v>
+        <v>5121</v>
       </c>
       <c r="D2" t="n">
-        <v>27739</v>
+        <v>19588</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3531</v>
+        <v>3495</v>
       </c>
       <c r="C3" t="n">
-        <v>4375</v>
+        <v>4440</v>
       </c>
       <c r="D3" t="n">
-        <v>8027</v>
+        <v>5073</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1981</v>
+        <v>1818</v>
       </c>
       <c r="C4" t="n">
-        <v>4080</v>
+        <v>2515</v>
       </c>
       <c r="D4" t="n">
-        <v>2130</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="C5" t="n">
-        <v>2020</v>
+        <v>884</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5407</v>
+        <v>6929</v>
       </c>
       <c r="C2" t="n">
-        <v>9781</v>
+        <v>4006</v>
       </c>
       <c r="D2" t="n">
-        <v>27306</v>
+        <v>28028</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3390</v>
+        <v>3296</v>
       </c>
       <c r="C3" t="n">
-        <v>7321</v>
+        <v>4168</v>
       </c>
       <c r="D3" t="n">
-        <v>10458</v>
+        <v>6922</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2312</v>
+        <v>2235</v>
       </c>
       <c r="C4" t="n">
-        <v>4111</v>
+        <v>3516</v>
       </c>
       <c r="D4" t="n">
-        <v>3140</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1016</v>
+        <v>955</v>
       </c>
       <c r="C5" t="n">
-        <v>3045</v>
+        <v>1726</v>
       </c>
       <c r="D5" t="n">
-        <v>1324</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>1157</v>
+        <v>592</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6810</v>
+        <v>7022</v>
       </c>
       <c r="C2" t="n">
-        <v>5174</v>
+        <v>12662</v>
       </c>
       <c r="D2" t="n">
-        <v>21844</v>
+        <v>40405</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3156</v>
+        <v>3695</v>
       </c>
       <c r="C3" t="n">
-        <v>7012</v>
+        <v>3342</v>
       </c>
       <c r="D3" t="n">
-        <v>11555</v>
+        <v>9071</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1747</v>
+        <v>1716</v>
       </c>
       <c r="C4" t="n">
-        <v>4785</v>
+        <v>3183</v>
       </c>
       <c r="D4" t="n">
-        <v>3822</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="C5" t="n">
-        <v>2592</v>
+        <v>1943</v>
       </c>
       <c r="D5" t="n">
-        <v>1283</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C6" t="n">
-        <v>1407</v>
+        <v>791</v>
       </c>
       <c r="D6" t="n">
-        <v>770</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>468</v>
+        <v>300</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5333</v>
+        <v>5507</v>
       </c>
       <c r="C2" t="n">
-        <v>6997</v>
+        <v>6637</v>
       </c>
       <c r="D2" t="n">
-        <v>22942</v>
+        <v>43179</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4123</v>
+        <v>4513</v>
       </c>
       <c r="C3" t="n">
-        <v>5124</v>
+        <v>7637</v>
       </c>
       <c r="D3" t="n">
-        <v>12433</v>
+        <v>13903</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2142</v>
+        <v>2370</v>
       </c>
       <c r="C4" t="n">
-        <v>6010</v>
+        <v>3214</v>
       </c>
       <c r="D4" t="n">
-        <v>5264</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="C5" t="n">
-        <v>3776</v>
+        <v>2640</v>
       </c>
       <c r="D5" t="n">
-        <v>1719</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="C6" t="n">
-        <v>2061</v>
+        <v>1444</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>817</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C7" t="n">
-        <v>992</v>
+        <v>576</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>266</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4375</v>
+        <v>4597</v>
       </c>
       <c r="C2" t="n">
-        <v>8326</v>
+        <v>10338</v>
       </c>
       <c r="D2" t="n">
-        <v>22532</v>
+        <v>35839</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3874</v>
+        <v>4125</v>
       </c>
       <c r="C3" t="n">
-        <v>5312</v>
+        <v>6118</v>
       </c>
       <c r="D3" t="n">
-        <v>13338</v>
+        <v>17586</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2671</v>
+        <v>2972</v>
       </c>
       <c r="C4" t="n">
-        <v>5391</v>
+        <v>5694</v>
       </c>
       <c r="D4" t="n">
-        <v>6361</v>
+        <v>5707</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1424</v>
+        <v>1531</v>
       </c>
       <c r="C5" t="n">
-        <v>4898</v>
+        <v>2904</v>
       </c>
       <c r="D5" t="n">
-        <v>2313</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>2926</v>
+        <v>2070</v>
       </c>
       <c r="D6" t="n">
-        <v>985</v>
+        <v>919</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C7" t="n">
-        <v>1526</v>
+        <v>1035</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>672</v>
+        <v>421</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_58_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_58_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6070</v>
+        <v>1882</v>
       </c>
       <c r="C2" t="n">
-        <v>9779</v>
+        <v>2648</v>
       </c>
       <c r="D2" t="n">
-        <v>26980</v>
+        <v>12982</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3589</v>
+        <v>2719</v>
       </c>
       <c r="C3" t="n">
-        <v>7191</v>
+        <v>9132</v>
       </c>
       <c r="D3" t="n">
-        <v>19122</v>
+        <v>11270</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3034</v>
+        <v>1703</v>
       </c>
       <c r="C4" t="n">
-        <v>5799</v>
+        <v>11889</v>
       </c>
       <c r="D4" t="n">
-        <v>7700</v>
+        <v>5415</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1920</v>
+        <v>943</v>
       </c>
       <c r="C5" t="n">
-        <v>4235</v>
+        <v>5935</v>
       </c>
       <c r="D5" t="n">
-        <v>2484</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1025</v>
+        <v>371</v>
       </c>
       <c r="C6" t="n">
-        <v>2463</v>
+        <v>2008</v>
       </c>
       <c r="D6" t="n">
-        <v>1054</v>
+        <v>739</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>461</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>1541</v>
+        <v>721</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>705</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
+        <v>278</v>
+      </c>
+      <c r="D9" t="n">
         <v>322</v>
-      </c>
-      <c r="D9" t="n">
-        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7427</v>
+        <v>1731</v>
       </c>
       <c r="C2" t="n">
-        <v>8159</v>
+        <v>3670</v>
       </c>
       <c r="D2" t="n">
-        <v>25102</v>
+        <v>21519</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3813</v>
+        <v>1966</v>
       </c>
       <c r="C3" t="n">
-        <v>7363</v>
+        <v>5131</v>
       </c>
       <c r="D3" t="n">
-        <v>18905</v>
+        <v>10736</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2809</v>
+        <v>1884</v>
       </c>
       <c r="C4" t="n">
-        <v>6290</v>
+        <v>10186</v>
       </c>
       <c r="D4" t="n">
-        <v>9256</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2142</v>
+        <v>1140</v>
       </c>
       <c r="C5" t="n">
-        <v>4882</v>
+        <v>8897</v>
       </c>
       <c r="D5" t="n">
-        <v>3259</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1279</v>
+        <v>562</v>
       </c>
       <c r="C6" t="n">
-        <v>3214</v>
+        <v>3891</v>
       </c>
       <c r="D6" t="n">
-        <v>1249</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>628</v>
+        <v>187</v>
       </c>
       <c r="C7" t="n">
-        <v>1956</v>
+        <v>1320</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>262</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1058</v>
+        <v>516</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>483</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9648</v>
+        <v>947</v>
       </c>
       <c r="C2" t="n">
-        <v>9882</v>
+        <v>1625</v>
       </c>
       <c r="D2" t="n">
-        <v>32638</v>
+        <v>14647</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4271</v>
+        <v>1833</v>
       </c>
       <c r="C3" t="n">
-        <v>6819</v>
+        <v>4404</v>
       </c>
       <c r="D3" t="n">
-        <v>18458</v>
+        <v>11755</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2742</v>
+        <v>2068</v>
       </c>
       <c r="C4" t="n">
-        <v>6633</v>
+        <v>9107</v>
       </c>
       <c r="D4" t="n">
-        <v>10456</v>
+        <v>6895</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2152</v>
+        <v>1149</v>
       </c>
       <c r="C5" t="n">
-        <v>5328</v>
+        <v>10391</v>
       </c>
       <c r="D5" t="n">
-        <v>3992</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1480</v>
+        <v>416</v>
       </c>
       <c r="C6" t="n">
-        <v>3842</v>
+        <v>4880</v>
       </c>
       <c r="D6" t="n">
-        <v>1521</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>802</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2473</v>
+        <v>1252</v>
       </c>
       <c r="D7" t="n">
-        <v>762</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>356</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1399</v>
+        <v>476</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>697</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8674</v>
+        <v>687</v>
       </c>
       <c r="C2" t="n">
-        <v>6719</v>
+        <v>5078</v>
       </c>
       <c r="D2" t="n">
-        <v>26819</v>
+        <v>12158</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5028</v>
+        <v>1239</v>
       </c>
       <c r="C3" t="n">
-        <v>10406</v>
+        <v>2689</v>
       </c>
       <c r="D3" t="n">
-        <v>20222</v>
+        <v>11362</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1988</v>
+        <v>1748</v>
       </c>
       <c r="C4" t="n">
-        <v>8808</v>
+        <v>6612</v>
       </c>
       <c r="D4" t="n">
-        <v>9584</v>
+        <v>7591</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="C5" t="n">
-        <v>3765</v>
+        <v>9658</v>
       </c>
       <c r="D5" t="n">
-        <v>2563</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>633</v>
       </c>
       <c r="C6" t="n">
-        <v>2423</v>
+        <v>7414</v>
       </c>
       <c r="D6" t="n">
-        <v>746</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>1371</v>
+        <v>2804</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>683</v>
+        <v>781</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>68</v>
-      </c>
-      <c r="D14" t="n">
-        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5228</v>
+        <v>487</v>
       </c>
       <c r="C2" t="n">
-        <v>3700</v>
+        <v>3731</v>
       </c>
       <c r="D2" t="n">
-        <v>18486</v>
+        <v>9762</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5603</v>
+        <v>916</v>
       </c>
       <c r="C3" t="n">
-        <v>7989</v>
+        <v>3343</v>
       </c>
       <c r="D3" t="n">
-        <v>19954</v>
+        <v>10827</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2726</v>
+        <v>1465</v>
       </c>
       <c r="C4" t="n">
-        <v>9614</v>
+        <v>4932</v>
       </c>
       <c r="D4" t="n">
-        <v>11110</v>
+        <v>7976</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1522</v>
+        <v>1448</v>
       </c>
       <c r="C5" t="n">
-        <v>5949</v>
+        <v>8629</v>
       </c>
       <c r="D5" t="n">
-        <v>3410</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>882</v>
+        <v>766</v>
       </c>
       <c r="C6" t="n">
-        <v>3010</v>
+        <v>8476</v>
       </c>
       <c r="D6" t="n">
-        <v>933</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>1780</v>
+        <v>4260</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>900</v>
+        <v>1240</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4506</v>
+        <v>742</v>
       </c>
       <c r="C2" t="n">
-        <v>7371</v>
+        <v>4354</v>
       </c>
       <c r="D2" t="n">
-        <v>18650</v>
+        <v>12742</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4614</v>
+        <v>631</v>
       </c>
       <c r="C3" t="n">
-        <v>5297</v>
+        <v>3101</v>
       </c>
       <c r="D3" t="n">
-        <v>18413</v>
+        <v>9980</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3373</v>
+        <v>1103</v>
       </c>
       <c r="C4" t="n">
-        <v>8618</v>
+        <v>4144</v>
       </c>
       <c r="D4" t="n">
-        <v>12215</v>
+        <v>8171</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1805</v>
+        <v>1332</v>
       </c>
       <c r="C5" t="n">
-        <v>7606</v>
+        <v>6852</v>
       </c>
       <c r="D5" t="n">
-        <v>4489</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1060</v>
+        <v>943</v>
       </c>
       <c r="C6" t="n">
-        <v>4278</v>
+        <v>8462</v>
       </c>
       <c r="D6" t="n">
-        <v>1277</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>463</v>
+        <v>334</v>
       </c>
       <c r="C7" t="n">
-        <v>2327</v>
+        <v>5994</v>
       </c>
       <c r="D7" t="n">
-        <v>571</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1262</v>
+        <v>2364</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>575</v>
+        <v>703</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2685</v>
+        <v>510</v>
       </c>
       <c r="C2" t="n">
-        <v>3458</v>
+        <v>2369</v>
       </c>
       <c r="D2" t="n">
-        <v>13031</v>
+        <v>9276</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4465</v>
+        <v>949</v>
       </c>
       <c r="C3" t="n">
-        <v>5832</v>
+        <v>3674</v>
       </c>
       <c r="D3" t="n">
-        <v>18025</v>
+        <v>10968</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3718</v>
+        <v>1780</v>
       </c>
       <c r="C4" t="n">
-        <v>8182</v>
+        <v>6302</v>
       </c>
       <c r="D4" t="n">
-        <v>13008</v>
+        <v>8355</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1882</v>
+        <v>932</v>
       </c>
       <c r="C5" t="n">
-        <v>9008</v>
+        <v>11055</v>
       </c>
       <c r="D5" t="n">
-        <v>4755</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>858</v>
+        <v>308</v>
       </c>
       <c r="C6" t="n">
-        <v>5058</v>
+        <v>7781</v>
       </c>
       <c r="D6" t="n">
-        <v>1253</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2381</v>
+        <v>2316</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>946</v>
+        <v>688</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2989</v>
+        <v>374</v>
       </c>
       <c r="C2" t="n">
-        <v>4380</v>
+        <v>2501</v>
       </c>
       <c r="D2" t="n">
-        <v>22193</v>
+        <v>7481</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3201</v>
+        <v>657</v>
       </c>
       <c r="C3" t="n">
-        <v>4238</v>
+        <v>2703</v>
       </c>
       <c r="D3" t="n">
-        <v>16307</v>
+        <v>10041</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3542</v>
+        <v>1182</v>
       </c>
       <c r="C4" t="n">
-        <v>6984</v>
+        <v>4689</v>
       </c>
       <c r="D4" t="n">
-        <v>13383</v>
+        <v>8168</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2308</v>
+        <v>891</v>
       </c>
       <c r="C5" t="n">
-        <v>8542</v>
+        <v>7875</v>
       </c>
       <c r="D5" t="n">
-        <v>5798</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1117</v>
+        <v>315</v>
       </c>
       <c r="C6" t="n">
-        <v>6692</v>
+        <v>7565</v>
       </c>
       <c r="D6" t="n">
-        <v>1707</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>3476</v>
+        <v>3225</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1470</v>
+        <v>818</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>492</v>
+        <v>260</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>122</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2323</v>
+        <v>380</v>
       </c>
       <c r="C2" t="n">
-        <v>2989</v>
+        <v>6504</v>
       </c>
       <c r="D2" t="n">
-        <v>16094</v>
+        <v>11456</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2745</v>
+        <v>437</v>
       </c>
       <c r="C3" t="n">
-        <v>3901</v>
+        <v>2256</v>
       </c>
       <c r="D3" t="n">
-        <v>16282</v>
+        <v>8944</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3172</v>
+        <v>827</v>
       </c>
       <c r="C4" t="n">
-        <v>5932</v>
+        <v>3504</v>
       </c>
       <c r="D4" t="n">
-        <v>13469</v>
+        <v>8261</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2540</v>
+        <v>928</v>
       </c>
       <c r="C5" t="n">
-        <v>8138</v>
+        <v>6104</v>
       </c>
       <c r="D5" t="n">
-        <v>6478</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1311</v>
+        <v>518</v>
       </c>
       <c r="C6" t="n">
-        <v>7526</v>
+        <v>7638</v>
       </c>
       <c r="D6" t="n">
-        <v>2090</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>4469</v>
+        <v>5381</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1918</v>
+        <v>1934</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>561</v>
+        <v>503</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3602</v>
+        <v>516</v>
       </c>
       <c r="C2" t="n">
-        <v>10020</v>
+        <v>16694</v>
       </c>
       <c r="D2" t="n">
-        <v>13069</v>
+        <v>11796</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2189</v>
+        <v>342</v>
       </c>
       <c r="C3" t="n">
-        <v>3186</v>
+        <v>3745</v>
       </c>
       <c r="D3" t="n">
-        <v>15217</v>
+        <v>8690</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2629</v>
+        <v>575</v>
       </c>
       <c r="C4" t="n">
-        <v>4913</v>
+        <v>2808</v>
       </c>
       <c r="D4" t="n">
-        <v>13464</v>
+        <v>8127</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2534</v>
+        <v>803</v>
       </c>
       <c r="C5" t="n">
-        <v>7079</v>
+        <v>4729</v>
       </c>
       <c r="D5" t="n">
-        <v>7220</v>
+        <v>5076</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1576</v>
+        <v>639</v>
       </c>
       <c r="C6" t="n">
-        <v>7771</v>
+        <v>6779</v>
       </c>
       <c r="D6" t="n">
-        <v>2610</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>538</v>
+        <v>268</v>
       </c>
       <c r="C7" t="n">
-        <v>5575</v>
+        <v>6418</v>
       </c>
       <c r="D7" t="n">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>2792</v>
+        <v>3453</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1005</v>
+        <v>1105</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5211</v>
+        <v>6484</v>
       </c>
       <c r="C2" t="n">
-        <v>4525</v>
+        <v>11238</v>
       </c>
       <c r="D2" t="n">
-        <v>7456</v>
+        <v>11007</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2606</v>
+        <v>848</v>
       </c>
       <c r="C2" t="n">
-        <v>5771</v>
+        <v>12580</v>
       </c>
       <c r="D2" t="n">
-        <v>9723</v>
+        <v>10347</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3004</v>
+        <v>338</v>
       </c>
       <c r="C3" t="n">
-        <v>4997</v>
+        <v>8182</v>
       </c>
       <c r="D3" t="n">
-        <v>16244</v>
+        <v>8517</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3683</v>
+        <v>417</v>
       </c>
       <c r="C4" t="n">
-        <v>7264</v>
+        <v>3172</v>
       </c>
       <c r="D4" t="n">
-        <v>13753</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1503</v>
+        <v>661</v>
       </c>
       <c r="C5" t="n">
-        <v>10721</v>
+        <v>3755</v>
       </c>
       <c r="D5" t="n">
-        <v>6477</v>
+        <v>5312</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>497</v>
+        <v>650</v>
       </c>
       <c r="C6" t="n">
-        <v>6910</v>
+        <v>5850</v>
       </c>
       <c r="D6" t="n">
-        <v>2033</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>372</v>
       </c>
       <c r="C7" t="n">
-        <v>2736</v>
+        <v>6501</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>984</v>
+        <v>4642</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>316</v>
+        <v>2001</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>593</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>61</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5818</v>
+        <v>7032</v>
       </c>
       <c r="C2" t="n">
-        <v>5210</v>
+        <v>8247</v>
       </c>
       <c r="D2" t="n">
-        <v>10275</v>
+        <v>16863</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2215</v>
+        <v>2140</v>
       </c>
       <c r="C3" t="n">
-        <v>2316</v>
+        <v>4437</v>
       </c>
       <c r="D3" t="n">
-        <v>1951</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5155</v>
+        <v>3728</v>
       </c>
       <c r="C2" t="n">
-        <v>6549</v>
+        <v>8893</v>
       </c>
       <c r="D2" t="n">
-        <v>16325</v>
+        <v>22127</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3298</v>
+        <v>3876</v>
       </c>
       <c r="C3" t="n">
-        <v>3429</v>
+        <v>5779</v>
       </c>
       <c r="D3" t="n">
-        <v>3205</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="C4" t="n">
-        <v>1422</v>
+        <v>2816</v>
       </c>
       <c r="D4" t="n">
-        <v>1574</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4569</v>
+        <v>2711</v>
       </c>
       <c r="C2" t="n">
-        <v>5121</v>
+        <v>9880</v>
       </c>
       <c r="D2" t="n">
-        <v>19588</v>
+        <v>19762</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3495</v>
+        <v>3169</v>
       </c>
       <c r="C3" t="n">
-        <v>4440</v>
+        <v>6519</v>
       </c>
       <c r="D3" t="n">
-        <v>5073</v>
+        <v>7170</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1818</v>
+        <v>2116</v>
       </c>
       <c r="C4" t="n">
-        <v>2515</v>
+        <v>4521</v>
       </c>
       <c r="D4" t="n">
-        <v>1824</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="C5" t="n">
-        <v>884</v>
+        <v>1706</v>
       </c>
       <c r="D5" t="n">
-        <v>1224</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6929</v>
+        <v>2497</v>
       </c>
       <c r="C2" t="n">
-        <v>4006</v>
+        <v>12886</v>
       </c>
       <c r="D2" t="n">
-        <v>28028</v>
+        <v>18935</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3296</v>
+        <v>2439</v>
       </c>
       <c r="C3" t="n">
-        <v>4168</v>
+        <v>7229</v>
       </c>
       <c r="D3" t="n">
-        <v>6922</v>
+        <v>8668</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2235</v>
+        <v>2278</v>
       </c>
       <c r="C4" t="n">
-        <v>3516</v>
+        <v>5558</v>
       </c>
       <c r="D4" t="n">
-        <v>2343</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>955</v>
+        <v>1086</v>
       </c>
       <c r="C5" t="n">
-        <v>1726</v>
+        <v>3210</v>
       </c>
       <c r="D5" t="n">
-        <v>1296</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C6" t="n">
-        <v>592</v>
+        <v>1021</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7022</v>
+        <v>2207</v>
       </c>
       <c r="C2" t="n">
-        <v>12662</v>
+        <v>14944</v>
       </c>
       <c r="D2" t="n">
-        <v>40405</v>
+        <v>14746</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3695</v>
+        <v>2041</v>
       </c>
       <c r="C3" t="n">
-        <v>3342</v>
+        <v>8792</v>
       </c>
       <c r="D3" t="n">
-        <v>9071</v>
+        <v>9618</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1716</v>
+        <v>2042</v>
       </c>
       <c r="C4" t="n">
-        <v>3183</v>
+        <v>6324</v>
       </c>
       <c r="D4" t="n">
-        <v>2691</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>841</v>
+        <v>1425</v>
       </c>
       <c r="C5" t="n">
-        <v>1943</v>
+        <v>4307</v>
       </c>
       <c r="D5" t="n">
-        <v>1173</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>291</v>
+        <v>573</v>
       </c>
       <c r="C6" t="n">
-        <v>791</v>
+        <v>2102</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5507</v>
+        <v>4234</v>
       </c>
       <c r="C2" t="n">
-        <v>6637</v>
+        <v>9578</v>
       </c>
       <c r="D2" t="n">
-        <v>43179</v>
+        <v>23189</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4513</v>
+        <v>1750</v>
       </c>
       <c r="C3" t="n">
-        <v>7637</v>
+        <v>10232</v>
       </c>
       <c r="D3" t="n">
-        <v>13903</v>
+        <v>9669</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2370</v>
+        <v>1774</v>
       </c>
       <c r="C4" t="n">
-        <v>3214</v>
+        <v>7340</v>
       </c>
       <c r="D4" t="n">
-        <v>3956</v>
+        <v>4717</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1148</v>
+        <v>1503</v>
       </c>
       <c r="C5" t="n">
-        <v>2640</v>
+        <v>5185</v>
       </c>
       <c r="D5" t="n">
-        <v>1443</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>525</v>
+        <v>854</v>
       </c>
       <c r="C6" t="n">
-        <v>1444</v>
+        <v>3097</v>
       </c>
       <c r="D6" t="n">
-        <v>817</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>176</v>
+        <v>293</v>
       </c>
       <c r="C7" t="n">
-        <v>576</v>
+        <v>1297</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>266</v>
+        <v>454</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4597</v>
+        <v>3685</v>
       </c>
       <c r="C2" t="n">
-        <v>10338</v>
+        <v>6053</v>
       </c>
       <c r="D2" t="n">
-        <v>35839</v>
+        <v>18365</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4125</v>
+        <v>2704</v>
       </c>
       <c r="C3" t="n">
-        <v>6118</v>
+        <v>14038</v>
       </c>
       <c r="D3" t="n">
-        <v>17586</v>
+        <v>10826</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2972</v>
+        <v>1388</v>
       </c>
       <c r="C4" t="n">
-        <v>5694</v>
+        <v>9416</v>
       </c>
       <c r="D4" t="n">
-        <v>5707</v>
+        <v>4419</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1531</v>
+        <v>789</v>
       </c>
       <c r="C5" t="n">
-        <v>2904</v>
+        <v>3035</v>
       </c>
       <c r="D5" t="n">
-        <v>1881</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>2070</v>
+        <v>1271</v>
       </c>
       <c r="D6" t="n">
-        <v>919</v>
+        <v>641</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>310</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>1035</v>
+        <v>444</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>421</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
